--- a/artfynd/A 28382-2026 artfynd.xlsx
+++ b/artfynd/A 28382-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135068799</v>
+        <v>137492719</v>
       </c>
       <c r="B4" t="n">
-        <v>101380</v>
+        <v>101650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553306</v>
+        <v>553203</v>
       </c>
       <c r="R4" t="n">
-        <v>6521326</v>
+        <v>6521286</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,12 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,6 +1012,312 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137492719</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137492798</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Almstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>553214</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521317</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonatan Axelsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonatan Axelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137492798</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137492812</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Almstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>553260</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6521274</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonatan Axelsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonatan Axelsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137492812</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135068799</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101380</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Almstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>553306</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6521326</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonatan Axelsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonatan Axelsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135068799</t>
         </is>
@@ -1022,6 +1328,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28382-2026 artfynd.xlsx
+++ b/artfynd/A 28382-2026 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>137492719</v>
       </c>
       <c r="B4" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137492798</v>
       </c>
       <c r="B5" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>137492812</v>
       </c>
       <c r="B6" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
